--- a/experiment/Omni_2CH_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/Omni_2CH_bestx4/Test/results-B100/B100.xlsx
@@ -455,7 +455,7 @@
         <v>24.05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5727</v>
+        <v>0.5733</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.77</v>
+        <v>28.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8137</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.55</v>
+        <v>26.6</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8136</v>
+        <v>0.8148</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>30.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8492</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>26.27</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7115</v>
+        <v>0.7119</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.95</v>
+        <v>33.96</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8934</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7509</v>
+        <v>0.7514999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>23.11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5924</v>
+        <v>0.5937</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.47</v>
+        <v>27.49</v>
       </c>
       <c r="C10" t="n">
-        <v>0.787</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.33</v>
+        <v>29.35</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8031</v>
+        <v>0.8038</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.63</v>
+        <v>24.65</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7367</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.98</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7519</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.04</v>
+        <v>30.05</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8092</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.33</v>
+        <v>29.38</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8312</v>
+        <v>0.832</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.06</v>
+        <v>25.07</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6791</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.79</v>
+        <v>24.82</v>
       </c>
       <c r="C17" t="n">
-        <v>0.759</v>
+        <v>0.7608</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.74</v>
+        <v>34.77</v>
       </c>
       <c r="C18" t="n">
-        <v>0.893</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.07</v>
+        <v>33.11</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8951</v>
+        <v>0.8957000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.22</v>
+        <v>26.26</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7381</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="21">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.1</v>
+        <v>26.09</v>
       </c>
       <c r="C21" t="n">
         <v>0.8015</v>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.25</v>
+        <v>22.27</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6949</v>
+        <v>0.6976</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.89</v>
+        <v>23.94</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6286</v>
+        <v>0.6321</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.85</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5726</v>
+        <v>0.5734</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.63</v>
+        <v>26.65</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7954</v>
+        <v>0.7963</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.69</v>
+        <v>27.71</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8223</v>
+        <v>0.8234</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +780,7 @@
         <v>27.03</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8385</v>
+        <v>0.8388</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>27.74</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7363</v>
+        <v>0.7371</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.61</v>
+        <v>29.62</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8024</v>
+        <v>0.8031</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.62</v>
+        <v>32.7</v>
       </c>
       <c r="C30" t="n">
-        <v>0.901</v>
+        <v>0.9021</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>19.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5047</v>
+        <v>0.5054999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>29.78</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8171</v>
+        <v>0.8175</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.93</v>
+        <v>20.94</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4268</v>
+        <v>0.4288</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         <v>25.22</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6726</v>
+        <v>0.6734</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>24.47</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7588</v>
+        <v>0.7592</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.99</v>
+        <v>35.03</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8932</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.01</v>
+        <v>27.05</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7426</v>
+        <v>0.7436</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.93</v>
+        <v>27.94</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5133</v>
+        <v>0.5137</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.25</v>
+        <v>28.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7161</v>
+        <v>0.7171999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.51</v>
+        <v>28.54</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7473</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.37</v>
+        <v>36.4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9577</v>
+        <v>0.9581</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         <v>26.8</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7437</v>
+        <v>0.7443</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.9</v>
+        <v>25.89</v>
       </c>
       <c r="C43" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.79</v>
+        <v>26.82</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7621</v>
+        <v>0.7629</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.06</v>
+        <v>28.1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8768</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.81</v>
+        <v>24.83</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6808</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.73</v>
+        <v>34.74</v>
       </c>
       <c r="C47" t="n">
-        <v>0.872</v>
+        <v>0.8723</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.81</v>
+        <v>22.85</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6241</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.99</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6349</v>
+        <v>0.6358</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.26</v>
+        <v>27.3</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8756</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.18</v>
+        <v>32.19</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8401</v>
+        <v>0.8403</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.86</v>
+        <v>24.89</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6203</v>
+        <v>0.6214</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.61</v>
+        <v>22.63</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1131,7 @@
         <v>32.62</v>
       </c>
       <c r="C54" t="n">
-        <v>0.847</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.56</v>
+        <v>32.57</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8001</v>
+        <v>0.8004</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.81</v>
+        <v>27.85</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7783</v>
+        <v>0.7802</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.61</v>
+        <v>25.63</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6931</v>
+        <v>0.6943</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>21.46</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4246</v>
+        <v>0.4259</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.49</v>
+        <v>27.52</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7277</v>
+        <v>0.729</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.02</v>
+        <v>32.03</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7924</v>
+        <v>0.7925</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.25</v>
+        <v>31.27</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7856</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.77</v>
+        <v>31.78</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8155</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.9</v>
+        <v>28.93</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7915</v>
+        <v>0.7924</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.76</v>
+        <v>33.86</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9524</v>
+        <v>0.9528</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.35</v>
+        <v>24.37</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6734</v>
+        <v>0.6746</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.03</v>
+        <v>26.04</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6206</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.37</v>
+        <v>28.4</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7943</v>
+        <v>0.7952</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40.08</v>
+        <v>40.17</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9811</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.03</v>
+        <v>21.05</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5794</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.8</v>
+        <v>22.82</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6516</v>
+        <v>0.6526</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.97</v>
+        <v>28.99</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8116</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.52</v>
+        <v>30.58</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8183</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.47</v>
+        <v>25.48</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.5976</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>27.22</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6058</v>
+        <v>0.6063</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>26.31</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6967</v>
+        <v>0.6972</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.07</v>
+        <v>24.08</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6976</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.66</v>
+        <v>30.68</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7844</v>
+        <v>0.7848000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>23.66</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4784</v>
+        <v>0.4792</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.81</v>
+        <v>29.84</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8107</v>
+        <v>0.8117</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.73</v>
+        <v>32.77</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.76</v>
+        <v>29.77</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8184</v>
+        <v>0.8189</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.75</v>
+        <v>35.81</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9382</v>
+        <v>0.9388</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.52</v>
+        <v>28.54</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7173</v>
+        <v>0.7184</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.25</v>
+        <v>22.26</v>
       </c>
       <c r="C84" t="n">
-        <v>0.528</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.07</v>
+        <v>21.08</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6069</v>
+        <v>0.6091</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.57</v>
+        <v>25.62</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7896</v>
+        <v>0.7913</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="C87" t="n">
-        <v>0.602</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.39</v>
+        <v>27.4</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6957</v>
+        <v>0.6967</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.72</v>
+        <v>30.75</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8137</v>
+        <v>0.8147</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5602</v>
+        <v>0.5608</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.11</v>
+        <v>25.13</v>
       </c>
       <c r="C91" t="n">
-        <v>0.647</v>
+        <v>0.6486</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.12</v>
+        <v>29.14</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7147</v>
+        <v>0.7151</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.69</v>
+        <v>26.75</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7553</v>
+        <v>0.7569</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.84</v>
+        <v>30.88</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8784</v>
+        <v>0.8789</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>25.98</v>
+        <v>26.01</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7166</v>
+        <v>0.7178</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.25</v>
+        <v>26.23</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8062</v>
+        <v>0.8066</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.93</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3178</v>
+        <v>0.3181</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.02</v>
+        <v>27.03</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5614</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.33</v>
+        <v>26.34</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7801</v>
+        <v>0.7806999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.91</v>
+        <v>26.93</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7352</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.13</v>
+        <v>25.16</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7296</v>
+        <v>0.7312</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.58</v>
+        <v>27.6</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7365</v>
+        <v>0.7375</v>
       </c>
     </row>
   </sheetData>
